--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484246_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484246_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>B. ROS FERNANDEZ</t>
+          <t>R. PÉREZ GALINDO</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>1.2021</v>
+        <v>0.0965</v>
       </c>
       <c r="E2" t="n">
-        <v>2.1795</v>
+        <v>-0.4122</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.9774</v>
+        <v>0.5088</v>
       </c>
       <c r="G2" t="n">
-        <v>-2.2566</v>
+        <v>-1.5933</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.3551</v>
+        <v>-0.3262</v>
       </c>
       <c r="I2" t="n">
-        <v>-1.9015</v>
+        <v>-1.2671</v>
       </c>
       <c r="J2" t="n">
-        <v>-0.9582000000000001</v>
+        <v>-1.1137</v>
       </c>
       <c r="K2" t="n">
-        <v>0.2686</v>
+        <v>-0.3863</v>
       </c>
       <c r="L2" t="n">
-        <v>-1.2268</v>
+        <v>-0.7274</v>
       </c>
       <c r="M2" t="n">
-        <v>-1.2984</v>
+        <v>-0.4795</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.6237</v>
+        <v>0.0601</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.6747</v>
+        <v>-0.5397</v>
       </c>
       <c r="P2" t="n">
-        <v>1.3674</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>-0.9767</v>
       </c>
       <c r="R2" t="n">
-        <v>1.3674</v>
+        <v>0.9767</v>
       </c>
       <c r="S2" t="n">
-        <v>1.482</v>
+        <v>0.7484</v>
       </c>
       <c r="T2" t="n">
-        <v>1.3098</v>
+        <v>0.4596</v>
       </c>
       <c r="U2" t="n">
-        <v>0.1722</v>
+        <v>0.2888</v>
       </c>
       <c r="V2" t="n">
-        <v>0.6093</v>
+        <v>0.9414</v>
       </c>
       <c r="W2" t="n">
-        <v>1.8279</v>
+        <v>1.2186</v>
       </c>
       <c r="X2" t="n">
-        <v>-1.2186</v>
+        <v>-0.2772</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>R. PÉREZ GALINDO</t>
+          <t>B. ROS FERNANDEZ</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.501</v>
+        <v>0.016</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.0078</v>
+        <v>0.9661999999999999</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5088</v>
+        <v>-0.9502</v>
       </c>
       <c r="G3" t="n">
-        <v>-1.5933</v>
+        <v>-2.2566</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.3262</v>
+        <v>-0.3551</v>
       </c>
       <c r="I3" t="n">
-        <v>-1.2671</v>
+        <v>-1.9015</v>
       </c>
       <c r="J3" t="n">
-        <v>-1.1137</v>
+        <v>-0.9582000000000001</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.3863</v>
+        <v>0.2686</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.7274</v>
+        <v>-1.2268</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.4795</v>
+        <v>-1.2984</v>
       </c>
       <c r="N3" t="n">
-        <v>0.0601</v>
+        <v>-0.6237</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.5397</v>
+        <v>-0.6747</v>
       </c>
       <c r="P3" t="n">
+        <v>1.3674</v>
+      </c>
+      <c r="Q3" t="n">
         <v>0</v>
       </c>
-      <c r="Q3" t="n">
-        <v>-0.9767</v>
-      </c>
       <c r="R3" t="n">
-        <v>0.9767</v>
+        <v>1.3674</v>
       </c>
       <c r="S3" t="n">
-        <v>1.1529</v>
+        <v>0.2958</v>
       </c>
       <c r="T3" t="n">
-        <v>0.864</v>
+        <v>0.0964</v>
       </c>
       <c r="U3" t="n">
-        <v>0.2888</v>
+        <v>0.1994</v>
       </c>
       <c r="V3" t="n">
-        <v>0.9414</v>
+        <v>0.6093</v>
       </c>
       <c r="W3" t="n">
-        <v>1.2186</v>
+        <v>1.8279</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.2772</v>
+        <v>-1.2186</v>
       </c>
     </row>
     <row r="4">
@@ -721,10 +721,10 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.2969</v>
+        <v>-0.6002999999999999</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.6874</v>
+        <v>-0.9907</v>
       </c>
       <c r="F4" t="n">
         <v>0.3904</v>
@@ -766,10 +766,10 @@
         <v>1.3674</v>
       </c>
       <c r="S4" t="n">
-        <v>0.7484</v>
+        <v>0.4451</v>
       </c>
       <c r="T4" t="n">
-        <v>0.6219</v>
+        <v>0.3186</v>
       </c>
       <c r="U4" t="n">
         <v>0.1265</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>M. FENÉS HERNÁNDEZ</t>
+          <t>I. MAYO SCHWANDT</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,64 +799,64 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-1.0919</v>
+        <v>-0.7953</v>
       </c>
       <c r="E5" t="n">
-        <v>0.4401</v>
+        <v>-0.9853</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.532</v>
+        <v>0.19</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0634</v>
+        <v>2.0785</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.9619</v>
+        <v>-1.671</v>
       </c>
       <c r="I5" t="n">
-        <v>1.0253</v>
+        <v>3.7495</v>
       </c>
       <c r="J5" t="n">
-        <v>0.6822</v>
+        <v>2.6017</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0614</v>
+        <v>0.06519999999999999</v>
       </c>
       <c r="L5" t="n">
-        <v>0.6208</v>
+        <v>2.5365</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.6188</v>
+        <v>-0.5232</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.0233</v>
+        <v>-1.7362</v>
       </c>
       <c r="O5" t="n">
-        <v>0.4045</v>
+        <v>1.213</v>
       </c>
       <c r="P5" t="n">
-        <v>0.3907</v>
+        <v>-2.5395</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-4.8836</v>
       </c>
       <c r="R5" t="n">
-        <v>0.3907</v>
+        <v>2.3441</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.0501</v>
+        <v>-0.0571</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.2421</v>
+        <v>0.078</v>
       </c>
       <c r="U5" t="n">
-        <v>0.192</v>
+        <v>-0.135</v>
       </c>
       <c r="V5" t="n">
-        <v>-1.4959</v>
+        <v>-0.2772</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.2186</v>
       </c>
       <c r="X5" t="n">
         <v>-1.4959</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>I. MAYO SCHWANDT</t>
+          <t>M. FENÉS HERNÁNDEZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,64 +877,64 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.2913</v>
+        <v>-0.9441000000000001</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.7536</v>
+        <v>0.6423</v>
       </c>
       <c r="F6" t="n">
-        <v>0.4623</v>
+        <v>-1.5865</v>
       </c>
       <c r="G6" t="n">
-        <v>2.0785</v>
+        <v>0.0634</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.671</v>
+        <v>-0.9619</v>
       </c>
       <c r="I6" t="n">
-        <v>3.7495</v>
+        <v>1.0253</v>
       </c>
       <c r="J6" t="n">
-        <v>2.6017</v>
+        <v>0.6822</v>
       </c>
       <c r="K6" t="n">
-        <v>0.06519999999999999</v>
+        <v>0.0614</v>
       </c>
       <c r="L6" t="n">
-        <v>2.5365</v>
+        <v>0.6208</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.5232</v>
+        <v>-0.6188</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.7362</v>
+        <v>-1.0233</v>
       </c>
       <c r="O6" t="n">
-        <v>1.213</v>
+        <v>0.4045</v>
       </c>
       <c r="P6" t="n">
-        <v>-2.5395</v>
+        <v>0.3907</v>
       </c>
       <c r="Q6" t="n">
-        <v>-4.8836</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>2.3441</v>
+        <v>0.3907</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.5531</v>
+        <v>0.0977</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.6904</v>
+        <v>-0.0399</v>
       </c>
       <c r="U6" t="n">
-        <v>0.1373</v>
+        <v>0.1375</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.2772</v>
+        <v>-1.4959</v>
       </c>
       <c r="W6" t="n">
-        <v>1.2186</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
         <v>-1.4959</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.687</v>
+        <v>-1.428</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.4579</v>
+        <v>-0.4985</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.2291</v>
+        <v>-0.9295</v>
       </c>
       <c r="G7" t="n">
         <v>0.5972</v>
@@ -1000,13 +1000,13 @@
         <v>1.5627</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.62</v>
+        <v>-0.361</v>
       </c>
       <c r="T7" t="n">
-        <v>0.1653</v>
+        <v>0.1247</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.7853</v>
+        <v>-0.4858</v>
       </c>
       <c r="V7" t="n">
         <v>-1.2735</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.1911</v>
+        <v>-1.9071</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.6071</v>
+        <v>-2.4048</v>
       </c>
       <c r="F8" t="n">
-        <v>0.416</v>
+        <v>0.4977</v>
       </c>
       <c r="G8" t="n">
         <v>-0.7887</v>
@@ -1078,13 +1078,13 @@
         <v>0.586</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.4573</v>
+        <v>-0.1733</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.3026</v>
+        <v>-0.1004</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.1546</v>
+        <v>-0.07290000000000001</v>
       </c>
       <c r="V8" t="n">
         <v>-0.5545</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.7164</v>
+        <v>-2.2163</v>
       </c>
       <c r="E9" t="n">
-        <v>-3.5788</v>
+        <v>-3.2149</v>
       </c>
       <c r="F9" t="n">
-        <v>0.8624000000000001</v>
+        <v>0.9986</v>
       </c>
       <c r="G9" t="n">
         <v>-1.5278</v>
@@ -1156,13 +1156,13 @@
         <v>1.5627</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.7979000000000001</v>
+        <v>-0.2978</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.2667</v>
+        <v>0.09719999999999999</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.5311</v>
+        <v>-0.395</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.2426</v>
+        <v>-3.8011</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.9852</v>
+        <v>-2.2169</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.2574</v>
+        <v>-1.5842</v>
       </c>
       <c r="G10" t="n">
         <v>-1.4908</v>
@@ -1234,13 +1234,13 @@
         <v>1.5627</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.1424</v>
+        <v>-0.7009</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.9408</v>
+        <v>-0.1725</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.2016</v>
+        <v>-0.5284</v>
       </c>
       <c r="V10" t="n">
         <v>-1.2186</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.5804</v>
+        <v>-4.5121</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.5661</v>
+        <v>-4.6067</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.0144</v>
+        <v>0.0946</v>
       </c>
       <c r="G11" t="n">
         <v>-2.1198</v>
@@ -1312,13 +1312,13 @@
         <v>0.9767</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.23</v>
+        <v>-0.1616</v>
       </c>
       <c r="T11" t="n">
-        <v>0.5147</v>
+        <v>0.4741</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.7446</v>
+        <v>-0.6357</v>
       </c>
       <c r="V11" t="n">
         <v>-0.2772</v>
@@ -1345,16 +1345,16 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-16.3945</v>
+        <v>-16.0918</v>
       </c>
       <c r="E12" t="n">
-        <v>-14.0243</v>
+        <v>-13.7215</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.3704</v>
+        <v>-2.3703</v>
       </c>
       <c r="G12" t="n">
-        <v>-7.532499999999999</v>
+        <v>-7.532500000000001</v>
       </c>
       <c r="H12" t="n">
         <v>-11.581</v>
@@ -1363,13 +1363,13 @@
         <v>4.0486</v>
       </c>
       <c r="J12" t="n">
-        <v>-3.2179</v>
+        <v>-3.217899999999999</v>
       </c>
       <c r="K12" t="n">
         <v>-3.2248</v>
       </c>
       <c r="L12" t="n">
-        <v>0.006900000000000128</v>
+        <v>0.00690000000000035</v>
       </c>
       <c r="M12" t="n">
         <v>-4.3144</v>
@@ -1390,13 +1390,13 @@
         <v>12.6971</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.4675000000000005</v>
+        <v>-0.1647</v>
       </c>
       <c r="T12" t="n">
-        <v>1.0331</v>
+        <v>1.3358</v>
       </c>
       <c r="U12" t="n">
-        <v>-1.5004</v>
+        <v>-1.5006</v>
       </c>
       <c r="V12" t="n">
         <v>-4.4876</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>6.9974</v>
+        <v>7.4498</v>
       </c>
       <c r="E13" t="n">
-        <v>3.3768</v>
+        <v>3.4779</v>
       </c>
       <c r="F13" t="n">
-        <v>3.6206</v>
+        <v>3.972</v>
       </c>
       <c r="G13" t="n">
         <v>3.322</v>
@@ -1468,13 +1468,13 @@
         <v>1.9534</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.2427</v>
+        <v>0.2097</v>
       </c>
       <c r="T13" t="n">
-        <v>0.08260000000000001</v>
+        <v>0.1838</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.3254</v>
+        <v>0.026</v>
       </c>
       <c r="V13" t="n">
         <v>2.16</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.6962</v>
+        <v>3.6043</v>
       </c>
       <c r="E14" t="n">
-        <v>1.7057</v>
+        <v>1.099</v>
       </c>
       <c r="F14" t="n">
-        <v>1.9905</v>
+        <v>2.5053</v>
       </c>
       <c r="G14" t="n">
         <v>0.8098</v>
@@ -1546,13 +1546,13 @@
         <v>2.7348</v>
       </c>
       <c r="S14" t="n">
-        <v>0.6092</v>
+        <v>0.5173</v>
       </c>
       <c r="T14" t="n">
-        <v>0.9933999999999999</v>
+        <v>0.3867</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.3842</v>
+        <v>0.1305</v>
       </c>
       <c r="V14" t="n">
         <v>1.4959</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>I. LLOVET CAMP</t>
+          <t>Q. SALVANS HIDALGO</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.597</v>
+        <v>3.2788</v>
       </c>
       <c r="E15" t="n">
-        <v>3.6195</v>
+        <v>1.4779</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.0225</v>
+        <v>1.8009</v>
       </c>
       <c r="G15" t="n">
-        <v>2.273</v>
+        <v>4.2602</v>
       </c>
       <c r="H15" t="n">
-        <v>2.7726</v>
+        <v>2.9663</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.4996</v>
+        <v>1.2939</v>
       </c>
       <c r="J15" t="n">
-        <v>2.8276</v>
+        <v>2.0482</v>
       </c>
       <c r="K15" t="n">
-        <v>2.7871</v>
+        <v>1.9672</v>
       </c>
       <c r="L15" t="n">
-        <v>0.0405</v>
+        <v>0.0809</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.5546</v>
+        <v>2.212</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.0146</v>
+        <v>0.999</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.5401</v>
+        <v>1.213</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>-0.1953</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.9767</v>
+        <v>-2.1488</v>
       </c>
       <c r="R15" t="n">
-        <v>0.9767</v>
+        <v>1.9534</v>
       </c>
       <c r="S15" t="n">
-        <v>1.324</v>
+        <v>0.1554</v>
       </c>
       <c r="T15" t="n">
-        <v>1.4914</v>
+        <v>0.08260000000000001</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.1674</v>
+        <v>0.0727</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>-0.9414</v>
       </c>
       <c r="W15" t="n">
-        <v>0.2772</v>
+        <v>1.4959</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.2772</v>
+        <v>-2.4373</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Q. SALVANS HIDALGO</t>
+          <t>I. LLOVET CAMP</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>3.1453</v>
+        <v>2.8425</v>
       </c>
       <c r="E16" t="n">
-        <v>1.4779</v>
+        <v>2.8106</v>
       </c>
       <c r="F16" t="n">
-        <v>1.6674</v>
+        <v>0.0319</v>
       </c>
       <c r="G16" t="n">
-        <v>4.2602</v>
+        <v>2.273</v>
       </c>
       <c r="H16" t="n">
-        <v>2.9663</v>
+        <v>2.7726</v>
       </c>
       <c r="I16" t="n">
-        <v>1.2939</v>
+        <v>-0.4996</v>
       </c>
       <c r="J16" t="n">
-        <v>2.0482</v>
+        <v>2.8276</v>
       </c>
       <c r="K16" t="n">
-        <v>1.9672</v>
+        <v>2.7871</v>
       </c>
       <c r="L16" t="n">
-        <v>0.0809</v>
+        <v>0.0405</v>
       </c>
       <c r="M16" t="n">
-        <v>2.212</v>
+        <v>-0.5546</v>
       </c>
       <c r="N16" t="n">
-        <v>0.999</v>
+        <v>-0.0146</v>
       </c>
       <c r="O16" t="n">
-        <v>1.213</v>
+        <v>-0.5401</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.1953</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>-2.1488</v>
+        <v>-0.9767</v>
       </c>
       <c r="R16" t="n">
-        <v>1.9534</v>
+        <v>0.9767</v>
       </c>
       <c r="S16" t="n">
-        <v>0.0219</v>
+        <v>0.5695</v>
       </c>
       <c r="T16" t="n">
-        <v>0.08260000000000001</v>
+        <v>0.6824</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.0607</v>
+        <v>-0.1129</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.9414</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>1.4959</v>
+        <v>0.2772</v>
       </c>
       <c r="X16" t="n">
-        <v>-2.4373</v>
+        <v>-0.2772</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2.662</v>
+        <v>2.2133</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.2798</v>
+        <v>-0.4821</v>
       </c>
       <c r="F17" t="n">
-        <v>2.9419</v>
+        <v>2.6954</v>
       </c>
       <c r="G17" t="n">
         <v>1.4266</v>
@@ -1780,13 +1780,13 @@
         <v>0.7814</v>
       </c>
       <c r="S17" t="n">
-        <v>1.0168</v>
+        <v>0.5681</v>
       </c>
       <c r="T17" t="n">
-        <v>0.2642</v>
+        <v>0.062</v>
       </c>
       <c r="U17" t="n">
-        <v>0.7526</v>
+        <v>0.5061</v>
       </c>
       <c r="V17" t="n">
         <v>0.6093</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.5946</v>
+        <v>1.9433</v>
       </c>
       <c r="E18" t="n">
-        <v>0.7756</v>
+        <v>1.18</v>
       </c>
       <c r="F18" t="n">
-        <v>0.8191000000000001</v>
+        <v>0.7632</v>
       </c>
       <c r="G18" t="n">
         <v>-1.8602</v>
@@ -1858,13 +1858,13 @@
         <v>2.5395</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.3032</v>
+        <v>0.0454</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.2337</v>
+        <v>0.1707</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.06950000000000001</v>
+        <v>-0.1253</v>
       </c>
       <c r="V18" t="n">
         <v>1.2186</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>1.2932</v>
+        <v>1.3412</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.2958</v>
+        <v>-0.5992</v>
       </c>
       <c r="F19" t="n">
-        <v>1.5891</v>
+        <v>1.9404</v>
       </c>
       <c r="G19" t="n">
         <v>3.9131</v>
@@ -1936,13 +1936,13 @@
         <v>0.9767</v>
       </c>
       <c r="S19" t="n">
-        <v>0.3103</v>
+        <v>0.3583</v>
       </c>
       <c r="T19" t="n">
-        <v>0.432</v>
+        <v>0.1287</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.1217</v>
+        <v>0.2297</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>J. OMOARUNA OSAZUWA</t>
+          <t>A. RUIZ CAÑAMERO</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>1.0124</v>
+        <v>1.2233</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.1193</v>
+        <v>0.191</v>
       </c>
       <c r="F20" t="n">
-        <v>1.1317</v>
+        <v>1.0324</v>
       </c>
       <c r="G20" t="n">
-        <v>0.6356000000000001</v>
+        <v>-0.1268</v>
       </c>
       <c r="H20" t="n">
-        <v>0.0156</v>
+        <v>-0.2612</v>
       </c>
       <c r="I20" t="n">
-        <v>0.62</v>
+        <v>0.1344</v>
       </c>
       <c r="J20" t="n">
-        <v>0.1014</v>
+        <v>-0.591</v>
       </c>
       <c r="K20" t="n">
-        <v>0.0205</v>
+        <v>-0.591</v>
       </c>
       <c r="L20" t="n">
-        <v>0.0809</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>0.5342</v>
+        <v>0.4642</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.0049</v>
+        <v>0.3298</v>
       </c>
       <c r="O20" t="n">
-        <v>0.5391</v>
+        <v>0.1344</v>
       </c>
       <c r="P20" t="n">
-        <v>0.3907</v>
+        <v>1.1721</v>
       </c>
       <c r="Q20" t="n">
         <v>-0.1953</v>
       </c>
       <c r="R20" t="n">
-        <v>0.586</v>
+        <v>1.3674</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.2911</v>
+        <v>-0.4313</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.3026</v>
+        <v>-0.2414</v>
       </c>
       <c r="U20" t="n">
-        <v>0.0115</v>
+        <v>-0.1899</v>
       </c>
       <c r="V20" t="n">
-        <v>0.2772</v>
+        <v>0.6093</v>
       </c>
       <c r="W20" t="n">
-        <v>0.2772</v>
+        <v>1.2186</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-0.6093</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A. RUIZ CAÑAMERO</t>
+          <t>J. OMOARUNA OSAZUWA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>0.8110000000000001</v>
+        <v>1.1329</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.1124</v>
+        <v>0.0829</v>
       </c>
       <c r="F21" t="n">
-        <v>0.9234</v>
+        <v>1.05</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.1268</v>
+        <v>0.6356000000000001</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.2612</v>
+        <v>0.0156</v>
       </c>
       <c r="I21" t="n">
-        <v>0.1344</v>
+        <v>0.62</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.591</v>
+        <v>0.1014</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.591</v>
+        <v>0.0205</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>0.0809</v>
       </c>
       <c r="M21" t="n">
-        <v>0.4642</v>
+        <v>0.5342</v>
       </c>
       <c r="N21" t="n">
-        <v>0.3298</v>
+        <v>-0.0049</v>
       </c>
       <c r="O21" t="n">
-        <v>0.1344</v>
+        <v>0.5391</v>
       </c>
       <c r="P21" t="n">
-        <v>1.1721</v>
+        <v>0.3907</v>
       </c>
       <c r="Q21" t="n">
         <v>-0.1953</v>
       </c>
       <c r="R21" t="n">
-        <v>1.3674</v>
+        <v>0.586</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.8436</v>
+        <v>-0.1706</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.5447</v>
+        <v>-0.1004</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.2989</v>
+        <v>-0.0702</v>
       </c>
       <c r="V21" t="n">
-        <v>0.6093</v>
+        <v>0.2772</v>
       </c>
       <c r="W21" t="n">
-        <v>1.2186</v>
+        <v>0.2772</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.6093</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>0.4092</v>
+        <v>0.7827</v>
       </c>
       <c r="E22" t="n">
-        <v>0.34</v>
+        <v>0.4411</v>
       </c>
       <c r="F22" t="n">
-        <v>0.0692</v>
+        <v>0.3416</v>
       </c>
       <c r="G22" t="n">
         <v>-0.2786</v>
@@ -2170,13 +2170,13 @@
         <v>0.9767</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.2888</v>
+        <v>0.08459999999999999</v>
       </c>
       <c r="T22" t="n">
-        <v>0.0689</v>
+        <v>0.17</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.3577</v>
+        <v>-0.0854</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-8.824</v>
+        <v>-8.069599999999999</v>
       </c>
       <c r="E23" t="n">
-        <v>-8.117800000000001</v>
+        <v>-7.3089</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.7062</v>
+        <v>-0.7607</v>
       </c>
       <c r="G23" t="n">
         <v>-6.8421</v>
@@ -2248,13 +2248,13 @@
         <v>1.7581</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.8452</v>
+        <v>-0.09080000000000001</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.8335</v>
+        <v>-0.0246</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.0117</v>
+        <v>-0.06619999999999999</v>
       </c>
       <c r="V23" t="n">
         <v>-0.9414</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>16.3943</v>
+        <v>17.7425</v>
       </c>
       <c r="E24" t="n">
-        <v>2.3704</v>
+        <v>2.370200000000001</v>
       </c>
       <c r="F24" t="n">
-        <v>14.0242</v>
+        <v>15.3724</v>
       </c>
       <c r="G24" t="n">
         <v>7.5326</v>
@@ -2296,13 +2296,13 @@
         <v>11.5811</v>
       </c>
       <c r="I24" t="n">
-        <v>-4.048500000000001</v>
+        <v>-4.0485</v>
       </c>
       <c r="J24" t="n">
         <v>4.314500000000001</v>
       </c>
       <c r="K24" t="n">
-        <v>8.356100000000001</v>
+        <v>8.3561</v>
       </c>
       <c r="L24" t="n">
         <v>-4.0417</v>
@@ -2326,13 +2326,13 @@
         <v>16.6041</v>
       </c>
       <c r="S24" t="n">
-        <v>0.4676</v>
+        <v>1.8156</v>
       </c>
       <c r="T24" t="n">
-        <v>1.5006</v>
+        <v>1.5005</v>
       </c>
       <c r="U24" t="n">
-        <v>-1.0331</v>
+        <v>0.3151</v>
       </c>
       <c r="V24" t="n">
         <v>4.4875</v>

--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484246_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484246_PROCESSED_CHRONO.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X24"/>
+  <dimension ref="A1:Y25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,11 +549,16 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>R. PÉREZ GALINDO</t>
+          <t>R. PEREZ GALINDO</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -626,6 +631,11 @@
       </c>
       <c r="X2" t="n">
         <v>-0.2772</v>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_2484246_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="3">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>-1.2186</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_2484246_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>-1.2186</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_2484246_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,11 +881,16 @@
       <c r="X5" t="n">
         <v>-1.4959</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_2484246_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>M. FENÉS HERNÁNDEZ</t>
+          <t>M. FENES HERNANDEZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -938,6 +963,11 @@
       </c>
       <c r="X6" t="n">
         <v>-1.4959</v>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_2484246_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="7">
@@ -1017,11 +1047,16 @@
       <c r="X7" t="n">
         <v>-1.2186</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_2484246_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>P. MARTÍNEZ FERIA</t>
+          <t>P. MARTINEZ FERIA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1094,6 +1129,11 @@
       </c>
       <c r="X8" t="n">
         <v>-0.5545</v>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_2484246_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="9">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>0</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_2484246_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>-1.4959</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_2484246_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>-0.2772</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_2484246_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,11 +1462,12 @@
       <c r="X12" t="n">
         <v>-9.252400000000002</v>
       </c>
+      <c r="Y12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>S. COSTA I VÁZQUEZ</t>
+          <t>S. COSTA I VAZQUEZ</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,31 +1479,31 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>7.4498</v>
+        <v>5.6219</v>
       </c>
       <c r="E13" t="n">
-        <v>3.4779</v>
+        <v>1.6499</v>
       </c>
       <c r="F13" t="n">
         <v>3.972</v>
       </c>
       <c r="G13" t="n">
-        <v>3.322</v>
+        <v>1.494</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.2384</v>
+        <v>-0.8524</v>
       </c>
       <c r="I13" t="n">
-        <v>3.5604</v>
+        <v>2.3464</v>
       </c>
       <c r="J13" t="n">
-        <v>1.9936</v>
+        <v>0.1656</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.4886</v>
+        <v>-1.1026</v>
       </c>
       <c r="L13" t="n">
-        <v>2.4822</v>
+        <v>1.2683</v>
       </c>
       <c r="M13" t="n">
         <v>1.3284</v>
@@ -1484,6 +1540,11 @@
       </c>
       <c r="X13" t="n">
         <v>0.6642</v>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_2484246_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="14">
@@ -1563,6 +1624,11 @@
       <c r="X14" t="n">
         <v>0</v>
       </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>play_by_play_2484246_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>-2.4373</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_2484246_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,6 +1790,11 @@
       <c r="X16" t="n">
         <v>-0.2772</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_2484246_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1797,6 +1873,11 @@
       <c r="X17" t="n">
         <v>-0.6093</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_2484246_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1875,11 +1956,16 @@
       <c r="X18" t="n">
         <v>-0.2772</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_2484246_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>T. SMALLWOOD</t>
+          <t>S. COSTA I VÁZQUEZ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,58 +1977,58 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>1.3412</v>
+        <v>1.8279</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.5992</v>
+        <v>1.8279</v>
       </c>
       <c r="F19" t="n">
-        <v>1.9404</v>
+        <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>3.9131</v>
+        <v>1.8279</v>
       </c>
       <c r="H19" t="n">
-        <v>2.888</v>
+        <v>0.614</v>
       </c>
       <c r="I19" t="n">
-        <v>1.0251</v>
+        <v>1.214</v>
       </c>
       <c r="J19" t="n">
-        <v>3.179</v>
+        <v>1.8279</v>
       </c>
       <c r="K19" t="n">
-        <v>2.5582</v>
+        <v>0.614</v>
       </c>
       <c r="L19" t="n">
-        <v>0.6208</v>
+        <v>1.214</v>
       </c>
       <c r="M19" t="n">
-        <v>0.734</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>0.3298</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>0.4043</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>-2.9301</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>-3.9069</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>0.9767</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>0.3583</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>0.1287</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>0.2297</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1952,12 +2038,17 @@
       </c>
       <c r="X19" t="n">
         <v>0</v>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_2484246_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A. RUIZ CAÑAMERO</t>
+          <t>T. SMALLWOOD</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +2060,78 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>1.2233</v>
+        <v>1.3412</v>
       </c>
       <c r="E20" t="n">
-        <v>0.191</v>
+        <v>-0.5992</v>
       </c>
       <c r="F20" t="n">
-        <v>1.0324</v>
+        <v>1.9404</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.1268</v>
+        <v>3.9131</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.2612</v>
+        <v>2.888</v>
       </c>
       <c r="I20" t="n">
-        <v>0.1344</v>
+        <v>1.0251</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.591</v>
+        <v>3.179</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.591</v>
+        <v>2.5582</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>0.6208</v>
       </c>
       <c r="M20" t="n">
-        <v>0.4642</v>
+        <v>0.734</v>
       </c>
       <c r="N20" t="n">
         <v>0.3298</v>
       </c>
       <c r="O20" t="n">
-        <v>0.1344</v>
+        <v>0.4043</v>
       </c>
       <c r="P20" t="n">
-        <v>1.1721</v>
+        <v>-2.9301</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.1953</v>
+        <v>-3.9069</v>
       </c>
       <c r="R20" t="n">
-        <v>1.3674</v>
+        <v>0.9767</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.4313</v>
+        <v>0.3583</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.2414</v>
+        <v>0.1287</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.1899</v>
+        <v>0.2297</v>
       </c>
       <c r="V20" t="n">
-        <v>0.6093</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>1.2186</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.6093</v>
+        <v>0</v>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_2484246_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>J. OMOARUNA OSAZUWA</t>
+          <t>A. RUIZ CANAMERO</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2143,78 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>1.1329</v>
+        <v>1.2233</v>
       </c>
       <c r="E21" t="n">
-        <v>0.0829</v>
+        <v>0.191</v>
       </c>
       <c r="F21" t="n">
-        <v>1.05</v>
+        <v>1.0324</v>
       </c>
       <c r="G21" t="n">
-        <v>0.6356000000000001</v>
+        <v>-0.1268</v>
       </c>
       <c r="H21" t="n">
-        <v>0.0156</v>
+        <v>-0.2612</v>
       </c>
       <c r="I21" t="n">
-        <v>0.62</v>
+        <v>0.1344</v>
       </c>
       <c r="J21" t="n">
-        <v>0.1014</v>
+        <v>-0.591</v>
       </c>
       <c r="K21" t="n">
-        <v>0.0205</v>
+        <v>-0.591</v>
       </c>
       <c r="L21" t="n">
-        <v>0.0809</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>0.5342</v>
+        <v>0.4642</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.0049</v>
+        <v>0.3298</v>
       </c>
       <c r="O21" t="n">
-        <v>0.5391</v>
+        <v>0.1344</v>
       </c>
       <c r="P21" t="n">
-        <v>0.3907</v>
+        <v>1.1721</v>
       </c>
       <c r="Q21" t="n">
         <v>-0.1953</v>
       </c>
       <c r="R21" t="n">
-        <v>0.586</v>
+        <v>1.3674</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.1706</v>
+        <v>-0.4313</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.1004</v>
+        <v>-0.2414</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.0702</v>
+        <v>-0.1899</v>
       </c>
       <c r="V21" t="n">
-        <v>0.2772</v>
+        <v>0.6093</v>
       </c>
       <c r="W21" t="n">
-        <v>0.2772</v>
+        <v>1.2186</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>-0.6093</v>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_2484246_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>R. CARRASCO SAGRISTA</t>
+          <t>J. OMOARUNA OSAZUWA</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2226,78 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>0.7827</v>
+        <v>1.1329</v>
       </c>
       <c r="E22" t="n">
-        <v>0.4411</v>
+        <v>0.0829</v>
       </c>
       <c r="F22" t="n">
-        <v>0.3416</v>
+        <v>1.05</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.2786</v>
+        <v>0.6356000000000001</v>
       </c>
       <c r="H22" t="n">
-        <v>2.6882</v>
+        <v>0.0156</v>
       </c>
       <c r="I22" t="n">
-        <v>-2.9668</v>
+        <v>0.62</v>
       </c>
       <c r="J22" t="n">
-        <v>0.2711</v>
+        <v>0.1014</v>
       </c>
       <c r="K22" t="n">
-        <v>2.2934</v>
+        <v>0.0205</v>
       </c>
       <c r="L22" t="n">
-        <v>-2.0223</v>
+        <v>0.0809</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.5498</v>
+        <v>0.5342</v>
       </c>
       <c r="N22" t="n">
-        <v>0.3948</v>
+        <v>-0.0049</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.9445</v>
+        <v>0.5391</v>
       </c>
       <c r="P22" t="n">
-        <v>0.9767</v>
+        <v>0.3907</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>-0.1953</v>
       </c>
       <c r="R22" t="n">
-        <v>0.9767</v>
+        <v>0.586</v>
       </c>
       <c r="S22" t="n">
-        <v>0.08459999999999999</v>
+        <v>-0.1706</v>
       </c>
       <c r="T22" t="n">
-        <v>0.17</v>
+        <v>-0.1004</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.0854</v>
+        <v>-0.0702</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>0.2772</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>0.2772</v>
       </c>
       <c r="X22" t="n">
         <v>0</v>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_2484246_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>M. SESE FRASNEDO</t>
+          <t>R. CARRASCO SAGRISTA</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2309,78 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-8.069599999999999</v>
+        <v>0.7827</v>
       </c>
       <c r="E23" t="n">
-        <v>-7.3089</v>
+        <v>0.4411</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.7607</v>
+        <v>0.3416</v>
       </c>
       <c r="G23" t="n">
-        <v>-6.8421</v>
+        <v>-0.2786</v>
       </c>
       <c r="H23" t="n">
-        <v>-2.2981</v>
+        <v>2.6882</v>
       </c>
       <c r="I23" t="n">
-        <v>-4.544</v>
+        <v>-2.9668</v>
       </c>
       <c r="J23" t="n">
-        <v>-5.6081</v>
+        <v>0.2711</v>
       </c>
       <c r="K23" t="n">
-        <v>-2.1438</v>
+        <v>2.2934</v>
       </c>
       <c r="L23" t="n">
-        <v>-3.4643</v>
+        <v>-2.0223</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.234</v>
+        <v>-0.5498</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.1542</v>
+        <v>0.3948</v>
       </c>
       <c r="O23" t="n">
-        <v>-1.0797</v>
+        <v>-0.9445</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.1953</v>
+        <v>0.9767</v>
       </c>
       <c r="Q23" t="n">
-        <v>-1.9534</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>1.7581</v>
+        <v>0.9767</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.09080000000000001</v>
+        <v>0.08459999999999999</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.0246</v>
+        <v>0.17</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.06619999999999999</v>
+        <v>-0.0854</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.9414</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>0.2772</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-1.2186</v>
+        <v>0</v>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_2484246_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>M. SESE FRASNEDO</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,68 +2392,152 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
+        <v>-8.069599999999999</v>
+      </c>
+      <c r="E24" t="n">
+        <v>-7.3089</v>
+      </c>
+      <c r="F24" t="n">
+        <v>-0.7607</v>
+      </c>
+      <c r="G24" t="n">
+        <v>-6.8421</v>
+      </c>
+      <c r="H24" t="n">
+        <v>-2.2981</v>
+      </c>
+      <c r="I24" t="n">
+        <v>-4.544</v>
+      </c>
+      <c r="J24" t="n">
+        <v>-5.6081</v>
+      </c>
+      <c r="K24" t="n">
+        <v>-2.1438</v>
+      </c>
+      <c r="L24" t="n">
+        <v>-3.4643</v>
+      </c>
+      <c r="M24" t="n">
+        <v>-1.234</v>
+      </c>
+      <c r="N24" t="n">
+        <v>-0.1542</v>
+      </c>
+      <c r="O24" t="n">
+        <v>-1.0797</v>
+      </c>
+      <c r="P24" t="n">
+        <v>-0.1953</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>-1.9534</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1.7581</v>
+      </c>
+      <c r="S24" t="n">
+        <v>-0.09080000000000001</v>
+      </c>
+      <c r="T24" t="n">
+        <v>-0.0246</v>
+      </c>
+      <c r="U24" t="n">
+        <v>-0.06619999999999999</v>
+      </c>
+      <c r="V24" t="n">
+        <v>-0.9414</v>
+      </c>
+      <c r="W24" t="n">
+        <v>0.2772</v>
+      </c>
+      <c r="X24" t="n">
+        <v>-1.2186</v>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_2484246_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>--- TOTAL ---</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>TQ-CB PRAT</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>1</v>
+      </c>
+      <c r="D25" t="n">
         <v>17.7425</v>
       </c>
-      <c r="E24" t="n">
-        <v>2.370200000000001</v>
-      </c>
-      <c r="F24" t="n">
+      <c r="E25" t="n">
+        <v>2.370100000000002</v>
+      </c>
+      <c r="F25" t="n">
         <v>15.3724</v>
       </c>
-      <c r="G24" t="n">
-        <v>7.5326</v>
-      </c>
-      <c r="H24" t="n">
+      <c r="G25" t="n">
+        <v>7.532499999999999</v>
+      </c>
+      <c r="H25" t="n">
         <v>11.5811</v>
       </c>
-      <c r="I24" t="n">
+      <c r="I25" t="n">
         <v>-4.0485</v>
       </c>
-      <c r="J24" t="n">
-        <v>4.314500000000001</v>
-      </c>
-      <c r="K24" t="n">
-        <v>8.3561</v>
-      </c>
-      <c r="L24" t="n">
-        <v>-4.0417</v>
-      </c>
-      <c r="M24" t="n">
+      <c r="J25" t="n">
+        <v>4.314400000000001</v>
+      </c>
+      <c r="K25" t="n">
+        <v>8.356100000000001</v>
+      </c>
+      <c r="L25" t="n">
+        <v>-4.041600000000001</v>
+      </c>
+      <c r="M25" t="n">
         <v>3.2178</v>
       </c>
-      <c r="N24" t="n">
+      <c r="N25" t="n">
         <v>3.2249</v>
       </c>
-      <c r="O24" t="n">
+      <c r="O25" t="n">
         <v>-0.006799999999999917</v>
       </c>
-      <c r="P24" t="n">
+      <c r="P25" t="n">
         <v>3.907099999999999</v>
       </c>
-      <c r="Q24" t="n">
+      <c r="Q25" t="n">
         <v>-12.6972</v>
       </c>
-      <c r="R24" t="n">
+      <c r="R25" t="n">
         <v>16.6041</v>
       </c>
-      <c r="S24" t="n">
+      <c r="S25" t="n">
         <v>1.8156</v>
       </c>
-      <c r="T24" t="n">
+      <c r="T25" t="n">
         <v>1.5005</v>
       </c>
-      <c r="U24" t="n">
+      <c r="U25" t="n">
         <v>0.3151</v>
       </c>
-      <c r="V24" t="n">
+      <c r="V25" t="n">
         <v>4.4875</v>
       </c>
-      <c r="W24" t="n">
+      <c r="W25" t="n">
         <v>9.252400000000002</v>
       </c>
-      <c r="X24" t="n">
+      <c r="X25" t="n">
         <v>-4.764699999999999</v>
       </c>
+      <c r="Y25" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
